--- a/Output/Final4/Validation-Individual.xlsx
+++ b/Output/Final4/Validation-Individual.xlsx
@@ -455,7 +455,7 @@
         <v>289</v>
       </c>
       <c r="E2" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -464,25 +464,25 @@
         <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>2385.72788673159</v>
+        <v>2385.72790186309</v>
       </c>
       <c r="I2" t="n">
-        <v>2345.43449781871</v>
+        <v>2345.43451346836</v>
       </c>
       <c r="J2" t="n">
-        <v>-11.0448174637776</v>
+        <v>-11.0448171458945</v>
       </c>
       <c r="K2" t="n">
-        <v>11.0448174637776</v>
+        <v>11.0448171458945</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0252609792264625</v>
+        <v>0.0248994352595842</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0299828338561803</v>
+        <v>0.0298156228976441</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0602647215586538</v>
+        <v>-0.0187377319978957</v>
       </c>
     </row>
     <row r="3">
@@ -499,7 +499,7 @@
         <v>289</v>
       </c>
       <c r="E3" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -520,13 +520,13 @@
         <v>9.8902144580946</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0125376912816203</v>
+        <v>0.0124287335103664</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0172200609040826</v>
+        <v>0.0172578874715865</v>
       </c>
       <c r="N3" t="n">
-        <v>0.803167079212744</v>
+        <v>0.803249930526333</v>
       </c>
     </row>
     <row r="4">
@@ -543,7 +543,7 @@
         <v>289</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -552,25 +552,25 @@
         <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>2437.81060121389</v>
+        <v>2437.81061213516</v>
       </c>
       <c r="I4" t="n">
-        <v>2423.35487296772</v>
+        <v>2423.35487271113</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.3818253284656</v>
+        <v>-10.3818256544245</v>
       </c>
       <c r="K4" t="n">
-        <v>10.3818253284656</v>
+        <v>10.3818256544245</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0512912835774472</v>
+        <v>0.0513984991777526</v>
       </c>
       <c r="M4" t="n">
-        <v>0.065921751716175</v>
+        <v>0.0659031943346525</v>
       </c>
       <c r="N4" t="n">
-        <v>0.366815775526143</v>
+        <v>0.359458031717805</v>
       </c>
     </row>
     <row r="5">
@@ -587,7 +587,7 @@
         <v>289</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -596,25 +596,25 @@
         <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>2373.37146062226</v>
+        <v>2373.37149637333</v>
       </c>
       <c r="I5" t="n">
-        <v>2332.97729374979</v>
+        <v>2332.97733154896</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.7232523990382</v>
+        <v>-10.7232505772126</v>
       </c>
       <c r="K5" t="n">
-        <v>10.7232523990382</v>
+        <v>10.7232505772126</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0242301450765601</v>
+        <v>0.0247496626900311</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0306809561591316</v>
+        <v>0.0315148627564691</v>
       </c>
       <c r="N5" t="n">
-        <v>0.245102866869075</v>
+        <v>-0.263609312767268</v>
       </c>
     </row>
     <row r="6">
@@ -631,7 +631,7 @@
         <v>289</v>
       </c>
       <c r="E6" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -640,25 +640,25 @@
         <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>2357.80005471134</v>
+        <v>2357.80004761035</v>
       </c>
       <c r="I6" t="n">
-        <v>2308.7884315016</v>
+        <v>2308.78841627565</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.55451638387464</v>
+        <v>-8.55451691294888</v>
       </c>
       <c r="K6" t="n">
-        <v>8.55451638387464</v>
+        <v>8.55451691294888</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0148763508200678</v>
+        <v>0.0149101175165019</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0241382811594192</v>
+        <v>0.0240084026289506</v>
       </c>
       <c r="N6" t="n">
-        <v>0.599982699859402</v>
+        <v>0.60431244835218</v>
       </c>
     </row>
     <row r="7">
@@ -675,7 +675,7 @@
         <v>289</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -684,25 +684,25 @@
         <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>1072.04666633253</v>
+        <v>1072.04688313371</v>
       </c>
       <c r="I7" t="n">
-        <v>4162.80979857294</v>
+        <v>4162.80993213459</v>
       </c>
       <c r="J7" t="n">
-        <v>-10.9857441009264</v>
+        <v>-10.985743372674</v>
       </c>
       <c r="K7" t="n">
-        <v>10.9857441009264</v>
+        <v>10.985743372674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0287409771613259</v>
+        <v>0.0290119988069231</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0382286299092272</v>
+        <v>0.0387948375112805</v>
       </c>
       <c r="N7" t="n">
-        <v>0.276962951970066</v>
+        <v>0.279954537471491</v>
       </c>
     </row>
     <row r="8">
@@ -719,7 +719,7 @@
         <v>291</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -728,25 +728,25 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>2419.7455133981</v>
+        <v>2419.74551441804</v>
       </c>
       <c r="I8" t="n">
-        <v>2374.85052318328</v>
+        <v>2374.85052621951</v>
       </c>
       <c r="J8" t="n">
-        <v>-10.8008556584094</v>
+        <v>-10.8008557439219</v>
       </c>
       <c r="K8" t="n">
-        <v>10.8008556584094</v>
+        <v>10.8008557439219</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0233838447343151</v>
+        <v>0.0232652979715056</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0298804425375809</v>
+        <v>0.0291827048404571</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.201115134152331</v>
+        <v>0.292228104631055</v>
       </c>
     </row>
     <row r="9">
@@ -763,7 +763,7 @@
         <v>291</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -772,25 +772,25 @@
         <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>2394.76150858628</v>
+        <v>2394.761509466</v>
       </c>
       <c r="I9" t="n">
-        <v>2337.43721799487</v>
+        <v>2337.43721344522</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.85073378735379</v>
+        <v>-8.85072951810411</v>
       </c>
       <c r="K9" t="n">
-        <v>8.85073378735379</v>
+        <v>8.85072951810411</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0142143344560584</v>
+        <v>0.0143453939103663</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0206957698837113</v>
+        <v>0.0208913590153202</v>
       </c>
       <c r="N9" t="n">
-        <v>0.740939310555433</v>
+        <v>0.736201578400577</v>
       </c>
     </row>
     <row r="10">
@@ -807,7 +807,7 @@
         <v>291</v>
       </c>
       <c r="E10" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -816,25 +816,25 @@
         <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>885.632782686067</v>
+        <v>885.632788237788</v>
       </c>
       <c r="I10" t="n">
-        <v>2839.4558667739</v>
+        <v>2839.45586390303</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.9335837906177</v>
+        <v>-11.9335837661152</v>
       </c>
       <c r="K10" t="n">
-        <v>11.9335837906177</v>
+        <v>11.9335837661152</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0507111971983921</v>
+        <v>0.0508526096382478</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0751728212828391</v>
+        <v>0.0754497227346396</v>
       </c>
       <c r="N10" t="n">
-        <v>0.164021045414376</v>
+        <v>0.156084612294662</v>
       </c>
     </row>
     <row r="11">
@@ -851,7 +851,7 @@
         <v>293</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -860,25 +860,25 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>2405.71953784311</v>
+        <v>2405.71951264918</v>
       </c>
       <c r="I11" t="n">
-        <v>2361.41023499524</v>
+        <v>2361.41019984881</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.9752122068958</v>
+        <v>-10.9752135157664</v>
       </c>
       <c r="K11" t="n">
-        <v>10.9752122068958</v>
+        <v>10.9752135157664</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0262449740256725</v>
+        <v>0.0261751373388364</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0326703748353269</v>
+        <v>0.0323491666805772</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.178870646481313</v>
+        <v>0.00704897744307227</v>
       </c>
     </row>
     <row r="12">
@@ -895,7 +895,7 @@
         <v>293</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -916,13 +916,13 @@
         <v>9.41184857917724</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0160214549850276</v>
+        <v>0.0160794978414248</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0241729052765332</v>
+        <v>0.0241165764590343</v>
       </c>
       <c r="N12" t="n">
-        <v>0.632374758303947</v>
+        <v>0.635571524604152</v>
       </c>
     </row>
     <row r="13">
@@ -939,7 +939,7 @@
         <v>293</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -948,25 +948,25 @@
         <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>1065.03434314981</v>
+        <v>1065.03430965372</v>
       </c>
       <c r="I13" t="n">
-        <v>4035.2030905807</v>
+        <v>4035.20304288959</v>
       </c>
       <c r="J13" t="n">
-        <v>-12.1332310130367</v>
+        <v>-12.133231258158</v>
       </c>
       <c r="K13" t="n">
-        <v>12.1332310130367</v>
+        <v>12.133231258158</v>
       </c>
       <c r="L13" t="n">
-        <v>0.045798371187545</v>
+        <v>0.0456077068526443</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0561314220750102</v>
+        <v>0.0560114380491086</v>
       </c>
       <c r="N13" t="n">
-        <v>0.232376911943193</v>
+        <v>0.275104205976566</v>
       </c>
     </row>
     <row r="14">
@@ -983,7 +983,7 @@
         <v>293</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1004,13 +1004,13 @@
         <v>10.9463002341762</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0316879676245557</v>
+        <v>0.0315500118750274</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0413160799652576</v>
+        <v>0.0414749232559228</v>
       </c>
       <c r="N14" t="n">
-        <v>0.033719994118376</v>
+        <v>-0.0275979682032282</v>
       </c>
     </row>
     <row r="15">
@@ -1027,7 +1027,7 @@
         <v>293</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1036,25 +1036,25 @@
         <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>2394.77606814116</v>
+        <v>2394.77605966508</v>
       </c>
       <c r="I15" t="n">
-        <v>2348.47022770983</v>
+        <v>2348.47020773099</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.14382702040799</v>
+        <v>-9.14383160049506</v>
       </c>
       <c r="K15" t="n">
-        <v>9.14382702040799</v>
+        <v>9.14383160049506</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0188462337084912</v>
+        <v>0.0186331626801914</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0298874070286409</v>
+        <v>0.0298590358270171</v>
       </c>
       <c r="N15" t="n">
-        <v>0.695577110633321</v>
+        <v>0.698304907498041</v>
       </c>
     </row>
     <row r="16">
@@ -1071,7 +1071,7 @@
         <v>293</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1080,25 +1080,25 @@
         <v>16</v>
       </c>
       <c r="H16" t="n">
-        <v>2097.66622815125</v>
+        <v>2097.66627614571</v>
       </c>
       <c r="I16" t="n">
-        <v>4182.75253830631</v>
+        <v>4182.75252828935</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.908961904804</v>
+        <v>-9.90896155448867</v>
       </c>
       <c r="K16" t="n">
-        <v>9.908961904804</v>
+        <v>9.90896155448867</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0285264957659699</v>
+        <v>0.028758931303331</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0494668490346843</v>
+        <v>0.0497831524527205</v>
       </c>
       <c r="N16" t="n">
-        <v>0.51870193785515</v>
+        <v>0.518400611219236</v>
       </c>
     </row>
   </sheetData>
